--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:15</t>
+    <t xml:space="preserve">2026-09-09 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:10</t>
+    <t xml:space="preserve">2026-09-17 14:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:06</t>
+    <t xml:space="preserve">2026-09-23 12:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:35</t>
+    <t xml:space="preserve">2026-10-02 14:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2021_maule.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:36</t>
+    <t xml:space="preserve">2026-10-05 10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -704,7 +704,7 @@
         <v>2021</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>225975.62</v>
+        <v>225975.63</v>
       </c>
     </row>
     <row r="11">
